--- a/human_validation/judge/kor/judge_D022_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D022_S003_P002__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,124 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 여기 온 건요... 너무 많이 먹고 나면, 체중이 늘지 않게 화장실에서 일부러 토를 해왔어요. 그게 심해져서, 솔직히 이걸 멈출 수 없을까 봐 무서워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 체중이나 체형이 본인 스스로를 보는 시각이나 자존감에 큰 영향을 준다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네... 그래요. 인정하고 싶은 것보다 훨씬 더요. 작업복 바지가 꽉 끼거나 거울에 비친 배를 보면, 제 자신에 대한 평가 전체가 확 떨어지는 것 같아요. 몸뿐만 아니라 모든 면에서 실패하고 있다는 기분이 들기 시작해요. 변속기도 척척 다루고 남자들이랑 어깨를 나란히 하던 그 강한 여자가 더 이상 아닌 것 같은 느낌이요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 한 자리에서 많은 양을 드시는 경우가 있나요? 같은 시간 동안 보통 사람들이 먹는 것보다 훨씬 많이, 그리고 일단 시작하면 멈출 수 없다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 주로 밤에, 집이 조용해지면 결국 부엌에 가서 거기 있는 건 뭐든 먹기 시작해요. 남은 음식, 시리얼, 과자, 아이스크림 같은 거요. 보통 식사량을 한참 넘어가고, 너무 많다는 걸 알면서도 계속 먹어요. 어떨 때는 멈추기 전에 식료품 저장고 절반은 없어진 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022) | 신경성 식욕부진증 (D021); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 저녁에 그렇게 드실 때, 먹는 양을 통제할 수 없다고 느끼시나요? 일단 시작하면 멈출 수 없는 것처럼요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 일단 시작하면 제가 통제하고 있는 게 아닌 것 같아요. 속으로 “Lucy, 그만해, 이제 됐어”라고 계속 말하는데도, 손은 계속 음식을 더 집어요. 다 끝나고 나서야 다시 제정신이 드는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022) | 신경성 식욕부진증 (D021); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 너무 많이 먹고 난 후 일부러 토를 하는 게 얼마나 자주 있으세요? 적어도 일주일에 한 번 정도인가요, 아니면 그보다 더 자주인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네... 적어도 일주일에 한 번은 있어요. 솔직히 지난 석 달 정도는, 그런 밤늦은 폭식 뒤에 그게 안 일어난 주가 거의 없었던 것 같아요. 어떤 주는 여러 번 그러기도 하는데, 특히 허리 때문에 집에 더 있을 때 그래요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022) | 신경성 식욕부진증 (D021); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>진단명: 신경성 폭식증 (D022)
 인구통계: 성별 여성 / 나이 45 / 직업상태 automotive service technician or mechanic / 최종학력 고등학교 졸업
@@ -575,191 +684,40 @@
 증상 지속 기간: 5 months
 추가 요건: The binge eating and inappropriate compensatory behaviors both occur, on average, at least once a week for 3 months
 주호소 증상 코드: S048
-배경 서술: Lucy는 정비소에서 까다로운 변속기 작업을 하다가 허리를 다쳤고, 그로 인해 한동안 무거운 물건을 들 수 없게 되면서 늘 자신을 강하고 유능하게 느끼게 해주던 몸을 쓰는 작업이 갑자기 줄어든 것에 좌절감을 느꼈다. 회복 기간 동안 “무리하지 말라”는 주변 사람들의 말과 체중이 늘까 봐 하는 스스로의 걱정 때문에 점점 더 자신의 몸에 집착하게 되었고, 다섯 달 사이에 활동량 없이 긴 하루를 보낸 뒤 밤늦게 먹는 습관이 통제할 수 없다고 느껴지는 반복적인 폭식으로 변해갔다. 그는 체중 증가를 막기 위해 구토를 하기 시작했고, 교회와 자동차 쇼, 가족 저녁 식사 자리에서는 말 많고 명랑한 모습으로 이 패턴을 숨기려 했지만, 빈도가 잦아지고 억누르기 어려워졌다. 남편이 식사 시간마다 느껴지는 긴장을 알아차렸고, Lucy가 더 이상 혼자서는 이 굴레를 멈출 수 없다고 인정하자 정신건강의학과 진료 예약을 잡는 것을 도왔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 여기 온 건요... 너무 많이 먹고 나면, 체중이 늘지 않게 화장실에서 일부러 토를 해왔어요. 그게 심해져서, 솔직히 이걸 멈출 수 없을까 봐 무서워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 체중이나 체형이 본인 스스로를 보는 시각이나 자존감에 큰 영향을 준다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네... 그래요. 인정하고 싶은 것보다 훨씬 더요. 작업복 바지가 꽉 끼거나 거울에 비친 배를 보면, 제 자신에 대한 평가 전체가 확 떨어지는 것 같아요. 몸뿐만 아니라 모든 면에서 실패하고 있다는 기분이 들기 시작해요. 변속기도 척척 다루고 남자들이랑 어깨를 나란히 하던 그 강한 여자가 더 이상 아닌 것 같은 느낌이요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 한 자리에서 많은 양을 드시는 경우가 있나요? 같은 시간 동안 보통 사람들이 먹는 것보다 훨씬 많이, 그리고 일단 시작하면 멈출 수 없다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 주로 밤에, 집이 조용해지면 결국 부엌에 가서 거기 있는 건 뭐든 먹기 시작해요. 남은 음식, 시리얼, 과자, 아이스크림 같은 거요. 보통 식사량을 한참 넘어가고, 너무 많다는 걸 알면서도 계속 먹어요. 어떨 때는 멈추기 전에 식료품 저장고 절반은 없어진 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 신경성 폭식증 (D022) | 중간확률: 신경성 식욕부진증 (D021); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 저녁에 그렇게 드실 때, 먹는 양을 통제할 수 없다고 느끼시나요? 일단 시작하면 멈출 수 없는 것처럼요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 일단 시작하면 제가 통제하고 있는 게 아닌 것 같아요. 속으로 “Lucy, 그만해, 이제 됐어”라고 계속 말하는데도, 손은 계속 음식을 더 집어요. 다 끝나고 나서야 다시 제정신이 드는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 신경성 폭식증 (D022) | 중간확률: 신경성 식욕부진증 (D021); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 너무 많이 먹고 난 후 일부러 토를 하는 게 얼마나 자주 있으세요? 적어도 일주일에 한 번 정도인가요, 아니면 그보다 더 자주인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네... 적어도 일주일에 한 번은 있어요. 솔직히 지난 석 달 정도는, 그런 밤늦은 폭식 뒤에 그게 안 일어난 주가 거의 없었던 것 같아요. 어떤 주는 여러 번 그러기도 하는데, 특히 허리 때문에 집에 더 있을 때 그래요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+배경 서술: Lucy는 정비소에서 까다로운 변속기 작업을 하다가 허리를 다쳤고, 그로 인해 한동안 무거운 물건을 들 수 없게 되면서 늘 자신을 강하고 유능하게 느끼게 해주던 몸을 쓰는 작업이 갑자기 줄어든 것에 좌절감을 느꼈다. 회복 기간 동안 “무리하지 말라”는 주변 사람들의 말과 체중이 늘까 봐 하는 스스로의 걱정 때문에 점점 더 자신의 몸에 집착하게 되었고, 다섯 달 사이에 활동량 없이 긴 하루를 보낸 뒤 밤늦게 먹는 습관이 통제할 수 없다고 느껴지는 반복적인 폭식으로 변해갔다. 그는 체중 증가를 막기 위해 구토를 하기 시작했고, 교회와 자동차 쇼, 가족 저녁 식사 자리에서는 말 많고 명랑한 모습으로 이 패턴을 숨기려 했지만, 빈도가 잦아지고 억누르기 어려워졌다. 남편이 식사 시간마다 느껴지는 긴장을 알아차렸고, Lucy가 더 이상 혼자서는 이 굴레를 멈출 수 없다고 인정하자 정신건강의학과 진료 예약을 잡는 것을 도왔다.
+표집된 증상 목록:
+  - S045 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.
+  - S046 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.
+  - S048 배출성 보상행동: 체중 증가를 막기 위해 음식이나 체액을 배출하는 반복적이고 부적절한 보상 행동.
+  - S049 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+  - S050 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).</t>
+        </is>
+      </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 신경성 폭식증 (D022) | 중간확률: 신경성 식욕부진증 (D021); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신경성 폭식증 (D022, ICD: F50.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.; 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
-  누락: (없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: compensatory_behavior (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 배출성 보상행동: 체중 증가를 막기 위해 음식이나 체액을 배출하는 반복적이고 부적절한 보상 행동.
-  누락: 비배출성 보상행동: 배출(음식물을 직접 제거하는 행위) 없이 체중 증가를 막기 위한 반복적이고 부적절한 보상 행동.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: body_image_cognition (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.
-  누락: 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.</t>
+          <t>의사의 최종 진단: 신경성 폭식증 (D022, ICD: F50.2)
+지속 기간 요건: 있음
+기능적 손상 요건: None
+추가 요건: 있음
+체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+  - 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
+체크리스트 그룹: compensatory_behavior (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 배출성 보상행동: 체중 증가를 막기 위해 음식이나 체액을 배출하는 반복적이고 부적절한 보상 행동.
+체크리스트 그룹: body_image_cognition (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D022_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D022_S003_P002__qwen3-235b_kor.xlsx
@@ -670,6 +670,11 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -713,11 +718,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D022_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D022_S003_P002__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.6333</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.7333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
